--- a/dist/test2.xlsx
+++ b/dist/test2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF93D75-64A2-4D8B-8312-76BB9600FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD3FE33-2E1E-4027-8094-28CB27D15691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="170">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -479,12 +479,448 @@
 # Выводим информацию о драконе
 dragon.display_info()</t>
   </si>
+  <si>
+    <t>Пройти игру</t>
+  </si>
+  <si>
+    <t>Космические</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Экономические</t>
+  </si>
+  <si>
+    <t>Основную игровую механику</t>
+  </si>
+  <si>
+    <t>шахматы -&gt; детерминированная игра
+камень/ножницы/бумага -&gt; недетерминированная игра
+крестики-нолики -&gt; детерминированная игра
+мафия -&gt; недетерминированная игра</t>
+  </si>
+  <si>
+    <t>Анализ геймплейных данных и обратная связь от игроков для определения дисбаланса и корректировки игровых параметров, Балансировка игровых уровней, чтобы они были сложными, но не непосильными для игроков., Балансировка игровой экономики, чтобы обеспечить равновесие между доходами и расходами в игре.</t>
+  </si>
+  <si>
+    <t>consumed = int(input())
+norm = int(input())
+if consumed &lt; norm:
+    print("Дефицит")
+elif consumed == norm:
+    print("Норма")
+else:
+    print("Избыток")</t>
+  </si>
+  <si>
+    <t>шахматы</t>
+  </si>
+  <si>
+    <t>Это уровень вовлеченности игрока, при котором он получает удовольствие от игры, не чувствуя ни скуки, ни непреодолимой сложности</t>
+  </si>
+  <si>
+    <t>Внутренняя мотивация связана с внутренними ценностями и удовлетворением от самого процесса выполнения задачи, в то время как внешняя мотивация приводит к выполнению задачи, учитывая внешние поощрения и наказания.</t>
+  </si>
+  <si>
+    <t>Прибор с кнопкой и отверстием, предназначенный для анализа реакции животного на поощрения</t>
+  </si>
+  <si>
+    <t>levels = 5
+for i in range(1, levels + 1):
+    spaces = ' ' * (levels - i)
+    print(spaces + '* ' * i)</t>
+  </si>
+  <si>
+    <t>Карьеристы (Достигатели)</t>
+  </si>
+  <si>
+    <t>Животные не перестают нажимать кнопку, пока получают вознаграждение, и делают это активнее, если вознаграждение непостоянно.</t>
+  </si>
+  <si>
+    <t>Кнопки джойстика -&gt; Элементы управления
+Карта -&gt; Информационные элементы
+Здоровье персонажа -&gt; Информационные элементы
+Клавиши клавиатуры -&gt; Элементы управления</t>
+  </si>
+  <si>
+    <t>UI отвечает за визуальное и функциональное оформление приложения, а UX - за взаимодействие пользователя с продуктом и его удовлетворенность от использования.</t>
+  </si>
+  <si>
+    <t>def analyze_ux(navigation_score, design_score):
+    score_to_text = {
+        1: "Плохо(",
+        2: "Хорошо)",
+        3: "Супер!"
+    }
+    min_score = min(navigation_score, design_score)
+    if navigation_score == design_score:
+        return score_to_text[navigation_score]
+    else:
+        return score_to_text[min_score]
+nav = int(input())
+design = int(input())
+result = analyze_ux(nav, design)
+print(result)</t>
+  </si>
+  <si>
+    <t>Head-Up Display — информация на экране, не требующая отрыва взгляда от основного действия. Понятие пришло из авиации.</t>
+  </si>
+  <si>
+    <t>UX-дизайнер</t>
+  </si>
+  <si>
+    <t>пользовательский путь</t>
+  </si>
+  <si>
+    <t>bits = int(input())
+colors = 2 ** bits
+print(colors)</t>
+  </si>
+  <si>
+    <t>Количество битов, используемых для определения цвета каждого пикселя.</t>
+  </si>
+  <si>
+    <t>Малое потребление памяти, что эффективно для устройств с ограниченными ресурсами.</t>
+  </si>
+  <si>
+    <t>Из каких этапов состоит путь пользователя в нашей игре?, Каких этапов не хватает для того, чтобы пользователю_x000B_было интересно и удобно играть?, Какие части игры необходимо улучшить?</t>
+  </si>
+  <si>
+    <t>Целевая аудитория</t>
+  </si>
+  <si>
+    <t>a = "Играть"
+b = "Выйти из игры"
+c = "Зайти в игру"
+d = "Выиграть или Проиграть"
+user_journey = [c, a, d, b]
+print(user_journey)</t>
+  </si>
+  <si>
+    <t>Пауза / Экран настроек</t>
+  </si>
+  <si>
+    <t>Разработка концепции UI (какие группы элементов нужны и как они связаны).</t>
+  </si>
+  <si>
+    <t>Спрайт – это основная единица, использующаяся при создании двумерных игр., Спрайт – двумерный графический элемент,_x000B_управляемый отдельно внутри системы, состоящей из множества других изображений.</t>
+  </si>
+  <si>
+    <t>Хитбокс – это невидимая область в виде прямоугольника или другой формы, которая определяет границы объекта</t>
+  </si>
+  <si>
+    <t>modules = ["pygame.display", "pygame.image", "pygame.event", "pygame.sprite"]
+assigments = ["обработка событий", "загрузка изображений", "создание объектов", "создание окна"]
+# Сопоставление по смыслу
+mapping = {
+    "pygame.display": "создание окна",
+    "pygame.image": "загрузка изображений",
+    "pygame.event": "обработка событий",
+    "pygame.sprite": "создание объектов"
+}
+result = []
+for i, module in enumerate(modules):
+    assignment = mapping[module]
+    j = assigments.index(assignment)
+    result.append(f"{i} {j}")
+print("\n".join(result), end="")</t>
+  </si>
+  <si>
+    <t>pygame.display</t>
+  </si>
+  <si>
+    <t>pip install pygame</t>
+  </si>
+  <si>
+    <t>Это бесконечный цикл, который продолжается в течение всего времени работы игры и обеспечивает обновление состояния игры, ввод от пользователя и отрисовку графики.</t>
+  </si>
+  <si>
+    <t>Модель, основанная на сочетании красного, зеленого и синего цветов.</t>
+  </si>
+  <si>
+    <t>class RGB:
+    def __init__(self, r, g, b):
+        self.r = r
+        self.g = g
+        self.b = b
+    def ratio(self):
+        print(round(self.r / 255, 2))
+        print(round(self.g / 255, 2))
+        print(round(self.b / 255, 2))
+r = int(input())
+g = int(input())
+b = int(input())
+color = RGB(r, g, b)
+color.ratio()</t>
+  </si>
+  <si>
+    <t>self.image.fill(GREEN)</t>
+  </si>
+  <si>
+    <t>pygame.QUIT</t>
+  </si>
+  <si>
+    <t>Совокупность элементов дизайна, которые позволяют взаимодействовать пользователю с программным обеспечением, игрой, приложением или сайтом.</t>
+  </si>
+  <si>
+    <t>24-битная глубина цвета позволяет использовать большее количество оттенков цвета.</t>
+  </si>
+  <si>
+    <t>row = int(input())
+col = int(input())
+for i in range(3):
+    for j in range(3):
+        if i == row and j == col:
+            print("X", end="")
+        else:
+            print("*", end="")
+    print()</t>
+  </si>
+  <si>
+    <t>К загруженному изображению (pygame.image.load("object.png"))</t>
+  </si>
+  <si>
+    <t>rect.collidepoint(event.pos)</t>
+  </si>
+  <si>
+    <t>a = pygame.mixer.Sound('file.mp3')</t>
+  </si>
+  <si>
+    <t>sound.play_sound()</t>
+  </si>
+  <si>
+    <t>x1 = int(input())
+x2 = int(input())
+y1 = int(input())
+y2 = int(input())
+if abs(x1 - x2) &lt;= 1 and abs(y1 - y2) &lt;= 1:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>pygame.mixer</t>
+  </si>
+  <si>
+    <t>self.active</t>
+  </si>
+  <si>
+    <t>За создание хитбокса</t>
+  </si>
+  <si>
+    <t>Движение на влево по оси X</t>
+  </si>
+  <si>
+    <t>solutions = []
+for x in range(1, 10001):   
+    if x**5 - 15*x**4 + 85*x**3 - 225*x**2 + 274*x - 120 == 0:       
+        solutions.append(x)
+solutions.sort()
+print(solutions)</t>
+  </si>
+  <si>
+    <t>Изменяет изображение объекта (self.image) в зависимости от нажатых клавиш-стрелок (вверх, вниз, влево, вправо).</t>
+  </si>
+  <si>
+    <t>В зависимости от комбинации нажатых стрелок выбирается соответствующее изображение (например, imageC для вверх+вправо, imageA для вниз+влево).</t>
+  </si>
+  <si>
+    <t>Для завершения работы игрового цикла после нажатия на крестик.</t>
+  </si>
+  <si>
+    <t>Группа для главного героя-лягушки и группа для всех падающих грибочков.</t>
+  </si>
+  <si>
+    <t>n = int(input())
+if n == 1 or n == 2 or n == 3:
+    print(1)
+else:
+    p1, p2, p3 = 1, 1, 1
+    for i in range(4, n + 1):
+        p_next = p1 + p2
+        p1, p2, p3 = p2, p3, p_next
+    print(p3)</t>
+  </si>
+  <si>
+    <t>коллизия</t>
+  </si>
+  <si>
+    <t>Грибы (mushroom_group) удаляются из группы при столкновении с лягушкой (frog).</t>
+  </si>
+  <si>
+    <t>В папке images</t>
+  </si>
+  <si>
+    <t>Программа завершит свою работу.</t>
+  </si>
+  <si>
+    <t>n = input()
+m = int(input())
+print(int(n[m - 1]))</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>from interface import *</t>
+  </si>
+  <si>
+    <t>x = int(input())
+y = int(input())
+z = int(input())
+if z == 2 * x**2 - 2 * y**2:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>get_rect</t>
+  </si>
+  <si>
+    <t>append</t>
+  </si>
+  <si>
+    <t>Отсутствует расширение png после имени файла</t>
+  </si>
+  <si>
+    <t>pygame.sprite.spritecollide(), pygame.sprite.collide_rect()</t>
+  </si>
+  <si>
+    <t>def is_leap_year(year):
+    if year % 400 == 0:
+        return True
+    elif year % 100 == 0:
+        return False
+    elif year % 4 == 0:
+        return True
+    else:
+        return False
+total = 0
+for year in range(0, 2025):
+    if is_leap_year(year):
+        total += year
+print(total)</t>
+  </si>
+  <si>
+    <t>Программа проверяет события PyGame и завершает работу, если пользователь закрывает окно.</t>
+  </si>
+  <si>
+    <t>Она перебирает все события, которые произошли в PyGame (нажатия клавиш, движение мыши, закрытие окна и т.д.).</t>
+  </si>
+  <si>
+    <t>Изменяется уровень здоровья Кукурузомена</t>
+  </si>
+  <si>
+    <t>if event.key == pygame.K_3</t>
+  </si>
+  <si>
+    <t>n = input()
+if len(n) != 2 or n[0] == '0' or int(n) &lt; 10 or int(n) &gt; 99:
+    print("ERROR")
+else:
+    digit1 = int(n[0])
+    digit2 = int(n[1])
+    max_digit = max(digit1, digit2)
+    min_digit = min(digit1, digit2)
+    print(max_digit, min_digit)</t>
+  </si>
+  <si>
+    <t>Задержка в 1 секунду (1000 миллисекунд), чтобы игрок увидел смену фона и состояние персонажа.</t>
+  </si>
+  <si>
+    <t>Временная смена фона на фоне лечения, отображение довольного состояния персонажа, задержка, возврат фона и изменение параметров (здоровье +2, сон -1, еда -1).</t>
+  </si>
+  <si>
+    <t>Будут созданы два объекта кнопок с изображениями и координатами, и они будут отображены на экране.</t>
+  </si>
+  <si>
+    <t>В строке 1 пропущено двоеточие в конце строки, В строке 2 пропущены координаты изображения</t>
+  </si>
+  <si>
+    <t>Чтобы указать, что игра вышла из режима паузы, и основной игровой цикл может продолжить работу.</t>
+  </si>
+  <si>
+    <t>count = 0
+prev = None
+while True:
+    num = int(input())
+    count += 1
+    if prev is not None and num == prev:
+        break
+    prev = num
+print(count)</t>
+  </si>
+  <si>
+    <t>Кнопки сна, здоровья и сытости становятся неактивны, появляются кнопки управления музыкой и выхода в главное меню, игровой таймер останавливается.</t>
+  </si>
+  <si>
+    <t>Графическая область на заднем плане игровой сцены, которая не является основным игровым элементом, но создает атмосферу и обеспечивает глубину и объемность игрового мира</t>
+  </si>
+  <si>
+    <t>меню</t>
+  </si>
+  <si>
+    <t>n = int(input())
+count = 0
+for i in range(1, n + 1):
+    num = int(input())
+    if i % 2 == 0 and num % 2 == 0:
+        count += 1
+print(count)</t>
+  </si>
+  <si>
+    <t>Арт-стиль, цветовая палитра, дизайн персонажей, фон, анимация и эффекты.</t>
+  </si>
+  <si>
+    <t>Рассказывает о характере, мотивациях и роли персонажа ещё до начала игры.</t>
+  </si>
+  <si>
+    <t>Создание игр в ретро-стиле</t>
+  </si>
+  <si>
+    <t>Применение перспективного вида</t>
+  </si>
+  <si>
+    <t>for num in range(100, 1000):
+    digits = str(num)
+    if len(set(digits)) == 3:
+        print(num)</t>
+  </si>
+  <si>
+    <t>Менять свою позицию или состояние, создавая иллюзию движения или изменения в игровом мире.</t>
+  </si>
+  <si>
+    <t>Изображение, которое кажется трёхмерным, но на самом деле является плоским.</t>
+  </si>
+  <si>
+    <t>(0,0,0)</t>
+  </si>
+  <si>
+    <t>Модель цветов, описывающая цвета при помощи оттенка, насыщенности и яркости</t>
+  </si>
+  <si>
+    <t>x1 = int(input())
+y1 = int(input())
+x2 = int(input())
+y2 = int(input())
+if (x1 + y1) % 2 == (x2 + y2) % 2:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>Отсутствие искажений при изменении размеров изображений.</t>
+  </si>
+  <si>
+    <t>Невозможность масштабирования без потерь.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +928,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri "/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -514,11 +955,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -833,13 +1275,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C187"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1">
         <v>11858</v>
       </c>
@@ -850,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>11858</v>
       </c>
@@ -861,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>11858</v>
       </c>
@@ -872,7 +1314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>11858</v>
       </c>
@@ -883,7 +1325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>11858</v>
       </c>
@@ -894,7 +1336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>11859</v>
       </c>
@@ -905,7 +1347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>11859</v>
       </c>
@@ -916,7 +1358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>11859</v>
       </c>
@@ -927,7 +1369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="150">
       <c r="A9">
         <v>11859</v>
       </c>
@@ -938,7 +1380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>11859</v>
       </c>
@@ -949,7 +1391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>11860</v>
       </c>
@@ -960,7 +1402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11860</v>
       </c>
@@ -971,7 +1413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>11860</v>
       </c>
@@ -982,7 +1424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="60">
       <c r="A14">
         <v>11860</v>
       </c>
@@ -993,7 +1435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>11860</v>
       </c>
@@ -1004,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>11861</v>
       </c>
@@ -1015,7 +1457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>11861</v>
       </c>
@@ -1026,7 +1468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>11861</v>
       </c>
@@ -1037,7 +1479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="165">
       <c r="A19">
         <v>11861</v>
       </c>
@@ -1048,7 +1490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>11861</v>
       </c>
@@ -1059,7 +1501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>11862</v>
       </c>
@@ -1070,7 +1512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>11862</v>
       </c>
@@ -1081,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>11862</v>
       </c>
@@ -1092,7 +1534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="150">
       <c r="A24">
         <v>11862</v>
       </c>
@@ -1103,7 +1545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>11862</v>
       </c>
@@ -1114,7 +1556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="409.5">
       <c r="A26">
         <v>11863</v>
       </c>
@@ -1125,7 +1567,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="409.5">
       <c r="A27">
         <v>11863</v>
       </c>
@@ -1136,7 +1578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>11863</v>
       </c>
@@ -1147,7 +1589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="120">
       <c r="A29">
         <v>11863</v>
       </c>
@@ -1158,7 +1600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>11863</v>
       </c>
@@ -1169,7 +1611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="150">
       <c r="A31">
         <v>11864</v>
       </c>
@@ -1180,7 +1622,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="120">
       <c r="A32">
         <v>11864</v>
       </c>
@@ -1191,7 +1633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="90">
       <c r="A33">
         <v>11864</v>
       </c>
@@ -1202,7 +1644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>11864</v>
       </c>
@@ -1213,7 +1655,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>11864</v>
       </c>
@@ -1224,7 +1666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="210">
       <c r="A36">
         <v>11865</v>
       </c>
@@ -1235,7 +1677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="90">
       <c r="A37">
         <v>11865</v>
       </c>
@@ -1246,7 +1688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="165">
       <c r="A38">
         <v>11865</v>
       </c>
@@ -1257,7 +1699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>11865</v>
       </c>
@@ -1268,7 +1710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>11865</v>
       </c>
@@ -1279,7 +1721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="150">
       <c r="A41">
         <v>11866</v>
       </c>
@@ -1290,7 +1732,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="195">
       <c r="A42">
         <v>11866</v>
       </c>
@@ -1301,7 +1743,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="150">
       <c r="A43">
         <v>11866</v>
       </c>
@@ -1312,7 +1754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>11866</v>
       </c>
@@ -1323,7 +1765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>11866</v>
       </c>
@@ -1334,7 +1776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="285">
       <c r="A46">
         <v>11867</v>
       </c>
@@ -1345,7 +1787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="210">
       <c r="A47">
         <v>11867</v>
       </c>
@@ -1356,7 +1798,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="135">
       <c r="A48">
         <v>11867</v>
       </c>
@@ -1367,7 +1809,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>11867</v>
       </c>
@@ -1378,7 +1820,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>11867</v>
       </c>
@@ -1389,7 +1831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="30">
       <c r="A51">
         <v>11868</v>
       </c>
@@ -1400,7 +1842,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="135">
       <c r="A52">
         <v>11868</v>
       </c>
@@ -1411,7 +1853,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="150">
       <c r="A53">
         <v>11868</v>
       </c>
@@ -1422,7 +1864,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>11869</v>
       </c>
@@ -1433,7 +1875,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="90">
       <c r="A55">
         <v>11869</v>
       </c>
@@ -1444,7 +1886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>11869</v>
       </c>
@@ -1455,7 +1897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>11869</v>
       </c>
@@ -1466,7 +1908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>11869</v>
       </c>
@@ -1477,7 +1919,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>11869</v>
       </c>
@@ -1488,7 +1930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="45">
       <c r="A60">
         <v>11871</v>
       </c>
@@ -1499,7 +1941,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>11871</v>
       </c>
@@ -1510,7 +1952,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>11871</v>
       </c>
@@ -1521,7 +1963,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>11872</v>
       </c>
@@ -1532,7 +1974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>11872</v>
       </c>
@@ -1543,7 +1985,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>11872</v>
       </c>
@@ -1554,7 +1996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="300">
       <c r="A66">
         <v>11873</v>
       </c>
@@ -1565,7 +2007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>11873</v>
       </c>
@@ -1576,7 +2018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>11873</v>
       </c>
@@ -1587,7 +2029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>11873</v>
       </c>
@@ -1598,7 +2040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>11873</v>
       </c>
@@ -1609,7 +2051,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>11873</v>
       </c>
@@ -1620,7 +2062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>11874</v>
       </c>
@@ -1631,7 +2073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>11874</v>
       </c>
@@ -1642,7 +2084,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>11874</v>
       </c>
@@ -1653,7 +2095,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="165">
       <c r="A75">
         <v>11874</v>
       </c>
@@ -1664,7 +2106,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>11875</v>
       </c>
@@ -1675,7 +2117,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>11875</v>
       </c>
@@ -1686,7 +2128,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="75">
       <c r="A78">
         <v>11875</v>
       </c>
@@ -1697,7 +2139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>11876</v>
       </c>
@@ -1708,7 +2150,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>11876</v>
       </c>
@@ -1719,7 +2161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="75">
       <c r="A81">
         <v>11876</v>
       </c>
@@ -1730,7 +2172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="255">
       <c r="A82">
         <v>11876</v>
       </c>
@@ -1741,7 +2183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="30">
       <c r="A83">
         <v>11877</v>
       </c>
@@ -1752,7 +2194,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>11877</v>
       </c>
@@ -1763,7 +2205,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>11877</v>
       </c>
@@ -1774,7 +2216,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>11877</v>
       </c>
@@ -1785,7 +2227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>11877</v>
       </c>
@@ -1796,7 +2238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>11878</v>
       </c>
@@ -1807,7 +2249,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="225">
       <c r="A89">
         <v>11878</v>
       </c>
@@ -1818,7 +2260,1086 @@
         <v>72</v>
       </c>
     </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>11881</v>
+      </c>
+      <c r="B90">
+        <v>1167953</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>11881</v>
+      </c>
+      <c r="B91">
+        <v>1167954</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>11881</v>
+      </c>
+      <c r="B92">
+        <v>1167955</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>11881</v>
+      </c>
+      <c r="B93">
+        <v>1201478</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>11881</v>
+      </c>
+      <c r="B94">
+        <v>1201479</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="60">
+      <c r="A95">
+        <v>11882</v>
+      </c>
+      <c r="B95">
+        <v>1167956</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="90">
+      <c r="A96">
+        <v>11882</v>
+      </c>
+      <c r="B96">
+        <v>1167957</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="135">
+      <c r="A97">
+        <v>11882</v>
+      </c>
+      <c r="B97">
+        <v>1167958</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>11882</v>
+      </c>
+      <c r="B98">
+        <v>1201483</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="45">
+      <c r="A99">
+        <v>11882</v>
+      </c>
+      <c r="B99">
+        <v>1201484</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="75">
+      <c r="A100">
+        <v>11883</v>
+      </c>
+      <c r="B100">
+        <v>1167959</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="30">
+      <c r="A101">
+        <v>11883</v>
+      </c>
+      <c r="B101">
+        <v>1167960</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="75">
+      <c r="A102">
+        <v>11883</v>
+      </c>
+      <c r="B102">
+        <v>1167961</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>11883</v>
+      </c>
+      <c r="B103">
+        <v>1201488</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="45">
+      <c r="A104">
+        <v>11883</v>
+      </c>
+      <c r="B104">
+        <v>1201489</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="60">
+      <c r="A105">
+        <v>11884</v>
+      </c>
+      <c r="B105">
+        <v>1167962</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="60">
+      <c r="A106">
+        <v>11884</v>
+      </c>
+      <c r="B106">
+        <v>1167963</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="300">
+      <c r="A107">
+        <v>11884</v>
+      </c>
+      <c r="B107">
+        <v>1167964</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="45">
+      <c r="A108">
+        <v>11884</v>
+      </c>
+      <c r="B108">
+        <v>1201493</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>11884</v>
+      </c>
+      <c r="B109">
+        <v>1201494</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>11885</v>
+      </c>
+      <c r="B110">
+        <v>1167965</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>11885</v>
+      </c>
+      <c r="B111">
+        <v>1167966</v>
+      </c>
+      <c r="C111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="75">
+      <c r="A112">
+        <v>11885</v>
+      </c>
+      <c r="B112">
+        <v>1167967</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="30">
+      <c r="A113">
+        <v>11885</v>
+      </c>
+      <c r="B113">
+        <v>1201499</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="30">
+      <c r="A114">
+        <v>11885</v>
+      </c>
+      <c r="B114">
+        <v>1201500</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="60">
+      <c r="A115">
+        <v>11886</v>
+      </c>
+      <c r="B115">
+        <v>1167968</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>11886</v>
+      </c>
+      <c r="B116">
+        <v>1167969</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="120">
+      <c r="A117">
+        <v>11886</v>
+      </c>
+      <c r="B117">
+        <v>1167970</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>11886</v>
+      </c>
+      <c r="B118">
+        <v>1201504</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="30">
+      <c r="A119">
+        <v>11886</v>
+      </c>
+      <c r="B119">
+        <v>1201505</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="60">
+      <c r="A120">
+        <v>11887</v>
+      </c>
+      <c r="B120">
+        <v>1167971</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>11887</v>
+      </c>
+      <c r="B121">
+        <v>1167972</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="300">
+      <c r="A122">
+        <v>11887</v>
+      </c>
+      <c r="B122">
+        <v>1167973</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>11887</v>
+      </c>
+      <c r="B123">
+        <v>1201510</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>11887</v>
+      </c>
+      <c r="B124">
+        <v>1201511</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="60">
+      <c r="A125">
+        <v>11888</v>
+      </c>
+      <c r="B125">
+        <v>1167974</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="30">
+      <c r="A126">
+        <v>11888</v>
+      </c>
+      <c r="B126">
+        <v>1167975</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="270">
+      <c r="A127">
+        <v>11888</v>
+      </c>
+      <c r="B127">
+        <v>1167976</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>11888</v>
+      </c>
+      <c r="B128">
+        <v>1201516</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>11888</v>
+      </c>
+      <c r="B129">
+        <v>1201517</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="45">
+      <c r="A130">
+        <v>11889</v>
+      </c>
+      <c r="B130">
+        <v>1167977</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="30">
+      <c r="A131">
+        <v>11889</v>
+      </c>
+      <c r="B131">
+        <v>1167978</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="150">
+      <c r="A132">
+        <v>11889</v>
+      </c>
+      <c r="B132">
+        <v>1167979</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="30">
+      <c r="A133">
+        <v>11889</v>
+      </c>
+      <c r="B133">
+        <v>1201521</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>11889</v>
+      </c>
+      <c r="B134">
+        <v>1201522</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>11890</v>
+      </c>
+      <c r="B135">
+        <v>1167980</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>11890</v>
+      </c>
+      <c r="B136">
+        <v>1167981</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="135">
+      <c r="A137">
+        <v>11890</v>
+      </c>
+      <c r="B137">
+        <v>1167982</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>11890</v>
+      </c>
+      <c r="B138">
+        <v>1201527</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>11890</v>
+      </c>
+      <c r="B139">
+        <v>1201528</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>11891</v>
+      </c>
+      <c r="B140">
+        <v>1167983</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>11891</v>
+      </c>
+      <c r="B141">
+        <v>1167984</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="90">
+      <c r="A142">
+        <v>11891</v>
+      </c>
+      <c r="B142">
+        <v>1167985</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="45">
+      <c r="A143">
+        <v>11891</v>
+      </c>
+      <c r="B143">
+        <v>1201813</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="45">
+      <c r="A144">
+        <v>11891</v>
+      </c>
+      <c r="B144">
+        <v>1201814</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="30">
+      <c r="A145">
+        <v>11892</v>
+      </c>
+      <c r="B145">
+        <v>1167986</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="30">
+      <c r="A146">
+        <v>11892</v>
+      </c>
+      <c r="B146">
+        <v>1167987</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="180">
+      <c r="A147">
+        <v>11892</v>
+      </c>
+      <c r="B147">
+        <v>1167988</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>11892</v>
+      </c>
+      <c r="B148">
+        <v>1201820</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="30">
+      <c r="A149">
+        <v>11892</v>
+      </c>
+      <c r="B149">
+        <v>1201821</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>11894</v>
+      </c>
+      <c r="B150">
+        <v>1167989</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>11894</v>
+      </c>
+      <c r="B151">
+        <v>1167990</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="45">
+      <c r="A152">
+        <v>11894</v>
+      </c>
+      <c r="B152">
+        <v>1167991</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>11895</v>
+      </c>
+      <c r="B153">
+        <v>1167992</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>11895</v>
+      </c>
+      <c r="B154">
+        <v>1167993</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="120">
+      <c r="A155">
+        <v>11895</v>
+      </c>
+      <c r="B155">
+        <v>1167994</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>11895</v>
+      </c>
+      <c r="B156">
+        <v>1201831</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>11895</v>
+      </c>
+      <c r="B157">
+        <v>1201832</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>11896</v>
+      </c>
+      <c r="B158">
+        <v>1167995</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>11896</v>
+      </c>
+      <c r="B159">
+        <v>1167996</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="240">
+      <c r="A160">
+        <v>11896</v>
+      </c>
+      <c r="B160">
+        <v>1167997</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="30">
+      <c r="A161">
+        <v>11896</v>
+      </c>
+      <c r="B161">
+        <v>1201836</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="45">
+      <c r="A162">
+        <v>11896</v>
+      </c>
+      <c r="B162">
+        <v>1201837</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>11897</v>
+      </c>
+      <c r="B163">
+        <v>1167998</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <v>11897</v>
+      </c>
+      <c r="B164">
+        <v>1167999</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="180">
+      <c r="A165">
+        <v>11897</v>
+      </c>
+      <c r="B165">
+        <v>1168000</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="30">
+      <c r="A166">
+        <v>11897</v>
+      </c>
+      <c r="B166">
+        <v>1201848</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="60">
+      <c r="A167">
+        <v>11897</v>
+      </c>
+      <c r="B167">
+        <v>1201852</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="30">
+      <c r="A168">
+        <v>11898</v>
+      </c>
+      <c r="B168">
+        <v>1168001</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="30">
+      <c r="A169">
+        <v>11898</v>
+      </c>
+      <c r="B169">
+        <v>1168002</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="195">
+      <c r="A170">
+        <v>11898</v>
+      </c>
+      <c r="B170">
+        <v>1168003</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="30">
+      <c r="A171">
+        <v>11898</v>
+      </c>
+      <c r="B171">
+        <v>1201866</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45">
+      <c r="A172">
+        <v>11898</v>
+      </c>
+      <c r="B172">
+        <v>1201866</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="60">
+      <c r="A173">
+        <v>11899</v>
+      </c>
+      <c r="B173">
+        <v>1168004</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>11899</v>
+      </c>
+      <c r="B174">
+        <v>1168005</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="135">
+      <c r="A175">
+        <v>11899</v>
+      </c>
+      <c r="B175">
+        <v>1168006</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="30">
+      <c r="A176">
+        <v>11899</v>
+      </c>
+      <c r="B176">
+        <v>1201871</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="30">
+      <c r="A177">
+        <v>11899</v>
+      </c>
+      <c r="B177">
+        <v>1201874</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <v>11900</v>
+      </c>
+      <c r="B178">
+        <v>1168007</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179">
+        <v>11900</v>
+      </c>
+      <c r="B179">
+        <v>1168008</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="60">
+      <c r="A180">
+        <v>11900</v>
+      </c>
+      <c r="B180">
+        <v>1168009</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="30">
+      <c r="A181">
+        <v>11900</v>
+      </c>
+      <c r="B181">
+        <v>1201881</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="30">
+      <c r="A182">
+        <v>11900</v>
+      </c>
+      <c r="B182">
+        <v>1201886</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183">
+        <v>11901</v>
+      </c>
+      <c r="B183">
+        <v>1168010</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="30">
+      <c r="A184">
+        <v>11901</v>
+      </c>
+      <c r="B184">
+        <v>1168011</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="135">
+      <c r="A185">
+        <v>11901</v>
+      </c>
+      <c r="B185">
+        <v>1168012</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="30">
+      <c r="A186">
+        <v>11901</v>
+      </c>
+      <c r="B186">
+        <v>1201894</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187">
+        <v>11901</v>
+      </c>
+      <c r="B187">
+        <v>1201895</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dist/test2.xlsx
+++ b/dist/test2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55C2A38-2566-48C1-8AB6-6554919E9006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3981F052-8C2D-4F5C-8F13-92E37C03E0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="14760" yWindow="3345" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1095,7 +1095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" ht="30">
       <c r="A24">
         <v>11908</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="30">
       <c r="A27">
         <v>11909</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" ht="30">
       <c r="A37">
         <v>11911</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" ht="30">
       <c r="A42">
         <v>11912</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" ht="30">
       <c r="A45">
         <v>11912</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" ht="45">
       <c r="A52">
         <v>11915</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" ht="30">
       <c r="A60">
         <v>11916</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" ht="30">
       <c r="A61">
         <v>11917</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" ht="30">
       <c r="A62">
         <v>11917</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" ht="30">
       <c r="A65">
         <v>11917</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" ht="30">
       <c r="A66">
         <v>11918</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" ht="30">
       <c r="A67">
         <v>11918</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" ht="30">
       <c r="A71">
         <v>11919</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" ht="30">
       <c r="A72">
         <v>11919</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" ht="30">
       <c r="A79">
         <v>11920</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" ht="30">
       <c r="A80">
         <v>11920</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" ht="30">
       <c r="A87">
         <v>11922</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" ht="30">
       <c r="A96">
         <v>11924</v>
       </c>
